--- a/stories/arbres/ATOM-SOC.ARG.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ce matin, maman a fini son travail. Elle rentre avec son sac. Louna l'attend près de la porte. Papa noue les lacets de Louna. Maman dit : j'ai travaillé. Avec le travail, on a de l'argent. L'argent sert à acheter. Ils vont à la boulangerie. Maman donne l'argent. Elle peut acheter du pain. Louna porte la baguette tiède. Plus tard, ils vont au marché. D'abord, les légumes. Des poireaux. Des tomates. Papa dit : l'argent sert aussi aux légumes. Louna pose une tomate dans le cabas. Ensuite, il y a des chaussures. Maman montre une paire. Elle dit : l'argent sert aux chaussures, quand on en a besoin. Louna touche le cuir souple. Papa range le reste. À la boulangerie, puis au marché, c'est pareil. Louna dit : le travail sert à acheter. Pain. Légumes. Chaussures.</t>
+          <t>Ce matin, maman a fini son travail. Elle rentre avec son sac. Louna l'attend près de la porte. Papa noue les lacets de Louna. J'ai travaillé. Avec le travail, on a de l'argent. L'argent sert à acheter. Ils vont à la boulangerie. Maman donne l'argent. Elle peut acheter du pain. Louna porte la baguette tiède. Plus tard, ils vont au marché. D'abord, les légumes. Des poireaux. Des tomates. L'argent sert aussi aux légumes. Louna pose une tomate dans le cabas. Ensuite, il y a des chaussures. Maman montre une paire. L'argent sert aux chaussures, quand on en a besoin. Louna touche le cuir souple. Papa range le reste. À la boulangerie, puis au marché, c'est pareil. Le travail sert à acheter. Pain. Légumes. Chaussures.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Ce matin, maman a fini son travail. Elle rentre avec son sac. Louna l'attend près de la porte. Papa noue les lacets de Louna.
+maman|J'ai travaillé. Avec le travail, on a de l'argent. L'argent sert à acheter. Ils vont à la boulangerie. Maman donne l'argent. Elle peut acheter du pain.
+narrateur|Louna porte la baguette tiède. Plus tard, ils vont au marché. D'abord, les légumes. Des poireaux. Des tomates.
+papa|L'argent sert aussi aux légumes.
+narrateur|Louna pose une tomate dans le cabas. Ensuite, il y a des chaussures. Maman montre une paire.
+narrateur|L'argent sert aux chaussures, quand on en a besoin.
+narrateur|Louna touche le cuir souple. Papa range le reste. À la boulangerie, puis au marché, c'est pareil.
+enfant-f|Le travail sert à acheter. Pain. Légumes. Chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Maman a travaillé. L'argent sert à quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Louna a compris. Le travail de maman sert. L'argent sert à acheter. Pain. Légumes. Chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|À la maison, Louna pose le pain. Papa range les légumes.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.ARG.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 enfant-f|Le travail sert à acheter. Pain. Légumes. Chaussures.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1510,7 @@
           <t>narrateur|Maman a travaillé. L'argent sert à quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1682,7 @@
           <t>narrateur|Louna a compris. Le travail de maman sert. L'argent sert à acheter. Pain. Légumes. Chaussures.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1846,7 @@
           <t>narrateur|À la maison, Louna pose le pain. Papa range les légumes.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.ARG.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Louna voit à quoi sert l'argent</t>
+          <t>Le fromage des halles</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sous les halles, la sciure colle aux semelles. Sarah veut un fromage, puis un fruit. Le gros fromage est trop grand ; une poire roule dans la sciure. Deux pièces, deux choses dans le cabas.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ce matin, maman a fini son travail. Elle rentre avec son sac. Louna l'attend près de la porte. Papa noue les lacets de Louna. J'ai travaillé. Avec le travail, on a de l'argent. L'argent sert à acheter. Ils vont à la boulangerie. Maman donne l'argent. Elle peut acheter du pain. Louna porte la baguette tiède. Plus tard, ils vont au marché. D'abord, les légumes. Des poireaux. Des tomates. L'argent sert aussi aux légumes. Louna pose une tomate dans le cabas. Ensuite, il y a des chaussures. Maman montre une paire. L'argent sert aux chaussures, quand on en a besoin. Louna touche le cuir souple. Papa range le reste. À la boulangerie, puis au marché, c'est pareil. Le travail sert à acheter. Pain. Légumes. Chaussures.</t>
+          <t>La sciure du sol colle aux semelles. Les piliers de fer sont froids, un peu verts. Ça sent le lait et les pommes, sous les halles. Un rayon tombe entre deux toiles. Papa porte un cabas de toile rêche. Maman range deux pièces dans sa poche. Sarah vit ici, avec maman et papa. Le sol fait un bruit de bois ! C'est la sciure. Tu as vu le stand du fromage ? Il est blanc, tout rond. Je veux un morceau. On y va. En ce moment, Sarah marche dans la sciure. Les copeaux collent à sa chaussure. Le stand du fromage est bas, en bois. Un gros fromage blanc attend sous une cloche. Celui-là, le gros. Il est trop grand pour nous. On prend un petit morceau ? Oui. Maman sort une pièce de la poche. La pièce brille un instant. Ça sert à prendre le fromage. La pièce tombe dans une boîte en fer. Ça sonne, tout court. Un petit triangle de fromage arrive. Il est enveloppé dans un papier huilé. Il sent le lait ! Oui. Tu le poses dans le cabas ? Oui, papa. Sarah pose le papier, tout doux. Le cabas devient un peu lourd. Je veux aussi un fruit. Plus loin, les poires. Elles avancent entre les piliers. La sciure marque leurs pas. Les poires sont jaunes, un peu tachetées. Celle-là, la brillante. Sarah montre une poire du doigt. La poire roule, tout d'un coup. Elle part dans la sciure. Elle est partie ! On la ramasse ensemble. Sarah se baisse près de papa. La poire a un peu de sciure dessus. Elle est encore belle. On en prend une autre, propre. J'ai encore une pièce. Papa tend la pièce. Le tiroir du fruitier sonne. Une poire propre passe dans le cabas. Elle est lourde. Oui. La pièce a servi à la prendre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ce matin, maman a fini son &lt;emphasis level="moderate"&gt;travail&lt;/emphasis&gt;. Elle rentre avec son sac. Louna l'attend près de la porte. Papa noue les lacets de Louna. Maman dit : j'ai travaillé. Avec le travail, on a de l'argent. L'argent sert à acheter. Ils vont à la boulangerie. Maman donne l'argent. Elle peut acheter du pain. Louna porte la baguette tiède. Plus tard, ils vont au marché. D'abord, les légumes. Des poireaux. Des tomates. Papa dit : l'argent sert aussi aux légumes. Louna pose une tomate dans le cabas. Ensuite, il y a des chaussures. Maman montre une paire. Elle dit : l'argent sert aux chaussures, quand on en a besoin. Louna touche le cuir souple. Papa range le reste. À la boulangerie, puis au marché, c'est pareil. Louna dit : le travail sert à acheter. Pain. Légumes. Chaussures.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La sciure du sol colle aux semelles. Les piliers de fer sont froids, un peu verts. Ça sent le lait et les pommes, sous les halles. Un rayon tombe entre deux toiles. Papa porte un cabas de toile rêche. Maman range deux pièces dans sa poche. Sarah vit ici, avec maman et papa. Le sol fait un bruit de bois ! C'est la sciure. Tu as vu le stand du fromage ? Il est blanc, tout rond. Je veux un morceau. On y va. En ce moment, Sarah marche dans la sciure. Les copeaux collent à sa chaussure. Le stand du fromage est bas, en bois. Un gros fromage blanc attend sous une cloche. Celui-là, le gros. Il est trop grand pour nous. On prend un petit morceau ? Oui. Maman sort une pièce de la poche. La pièce brille un instant. Ça sert à prendre le fromage. La pièce tombe dans une boîte en fer. Ça sonne, tout court. Un petit triangle de fromage arrive. Il est enveloppé dans un papier huilé. Il sent le lait ! Oui. Tu le poses dans le cabas ? Oui, papa. Sarah pose le papier, tout doux. Le cabas devient un peu lourd. Je veux aussi un fruit. Plus loin, les poires. Elles avancent entre les piliers. La sciure marque leurs pas. Les poires sont jaunes, un peu tachetées. Celle-là, la brillante. Sarah montre une poire du doigt. La poire roule, tout d'un coup. Elle part dans la sciure. Elle est partie ! On la ramasse ensemble. Sarah se baisse près de papa. La poire a un peu de sciure dessus. Elle est encore belle. On en prend une autre, propre. J'ai encore une pièce. Papa tend la pièce. Le tiroir du fruitier sonne. Une poire propre passe dans le cabas. Elle est lourde. Oui. La pièce a servi à la prendre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,17 +1324,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Ce matin, maman a fini son travail. Elle rentre avec son sac. Louna l'attend près de la porte. Papa noue les lacets de Louna.
-maman|J'ai travaillé. Avec le travail, on a de l'argent. L'argent sert à acheter. Ils vont à la boulangerie. Maman donne l'argent. Elle peut acheter du pain.
-narrateur|Louna porte la baguette tiède. Plus tard, ils vont au marché. D'abord, les légumes. Des poireaux. Des tomates.
-papa|L'argent sert aussi aux légumes.
-narrateur|Louna pose une tomate dans le cabas. Ensuite, il y a des chaussures. Maman montre une paire.
-narrateur|L'argent sert aux chaussures, quand on en a besoin.
-narrateur|Louna touche le cuir souple. Papa range le reste. À la boulangerie, puis au marché, c'est pareil.
-enfant-f|Le travail sert à acheter. Pain. Légumes. Chaussures.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La sciure du sol colle aux semelles.
+narrateur|Les piliers de fer sont froids, un peu verts.
+narrateur|Ça sent le lait et les pommes, sous les halles.
+narrateur|Un rayon tombe entre deux toiles.
+narrateur|Papa porte un cabas de toile rêche.
+narrateur|Maman range deux pièces dans sa poche.
+narrateur|Sarah vit ici, avec maman et papa.
+enfant-f|Le sol fait un bruit de bois !
+maman|C'est la sciure.
+papa|Tu as vu le stand du fromage ?
+enfant-f|Il est blanc, tout rond.
+enfant-f|Je veux un morceau.
+maman|On y va.
+narrateur|En ce moment, Sarah marche dans la sciure.
+narrateur|Les copeaux collent à sa chaussure.
+narrateur|Le stand du fromage est bas, en bois.
+narrateur|Un gros fromage blanc attend sous une cloche.
+enfant-f|Celui-là, le gros.
+papa|Il est trop grand pour nous.
+maman|On prend un petit morceau ?
+enfant-f|Oui.
+narrateur|Maman sort une pièce de la poche.
+narrateur|La pièce brille un instant.
+maman|Ça sert à prendre le fromage.
+narrateur|La pièce tombe dans une boîte en fer.
+narrateur|Ça sonne, tout court.
+narrateur|Un petit triangle de fromage arrive.
+narrateur|Il est enveloppé dans un papier huilé.
+enfant-f|Il sent le lait !
+papa|Oui.
+papa|Tu le poses dans le cabas ?
+enfant-f|Oui, papa.
+narrateur|Sarah pose le papier, tout doux.
+narrateur|Le cabas devient un peu lourd.
+enfant-f|Je veux aussi un fruit.
+maman|Plus loin, les poires.
+narrateur|Elles avancent entre les piliers.
+narrateur|La sciure marque leurs pas.
+narrateur|Les poires sont jaunes, un peu tachetées.
+enfant-f|Celle-là, la brillante.
+narrateur|Sarah montre une poire du doigt.
+narrateur|La poire roule, tout d'un coup.
+narrateur|Elle part dans la sciure.
+enfant-f|Elle est partie !
+papa|On la ramasse ensemble.
+narrateur|Sarah se baisse près de papa.
+narrateur|La poire a un peu de sciure dessus.
+enfant-f|Elle est encore belle.
+maman|On en prend une autre, propre.
+papa|J'ai encore une pièce.
+narrateur|Papa tend la pièce.
+narrateur|Le tiroir du fruitier sonne.
+narrateur|Une poire propre passe dans le cabas.
+enfant-f|Elle est lourde.
+maman|Oui.
+maman|La pièce a servi à la prendre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1347,12 +1406,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Maman a travaillé. L'argent sert à quoi ?</t>
+          <t>Maman et papa ont donné des pièces. L'argent sert à quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman a &lt;emphasis level="moderate"&gt;travail&lt;/emphasis&gt;lé. L'argent sert à quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman et papa ont donné des pièces. L'argent sert à quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1367,7 +1426,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>acheter | le pain | acheter du pain | le travail</t>
+          <t>acheter | le fromage | le fruit | la poire | les pièces | prendre</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1382,7 +1441,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>On achète du pain. L'argent sert à quoi ?</t>
+          <t>On prend le fromage et la poire. L'argent sert à quoi ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1424,14 +1483,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1507,10 +1566,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Maman a travaillé. L'argent sert à quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Maman et papa ont donné des pièces.
+narrateur|L'argent sert à quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1535,12 +1594,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Louna a compris. Le travail de maman sert. L'argent sert à acheter. Pain. Légumes. Chaussures.</t>
+          <t>Le cabas tient le fromage et la poire. Le papier huilé sent encore le lait. Les pièces ont servi à les prendre. Le fromage, puis le fruit. Oui. On achète avec ça. Sarah essuie un copeau de sciure. Il était collé à la semelle. Le sol était tout jaune. C'est les halles. Bravo, Sarah. Le pilier de fer reste froid. Un rayon glisse encore sur la toile. Tu as fini de porter le cabas ? Il est un peu lourd. On le porte à deux. Sarah tient une anse. Papa tient l'autre. La poire roule un peu, puis s'arrête. Elle reste. Oui. On rentre ? Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Louna a compris. Le &lt;emphasis level="moderate"&gt;travail&lt;/emphasis&gt; de maman sert. L'argent sert à acheter. Pain. Légumes. Chaussures.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le cabas tient le fromage et la poire. Le papier huilé sent encore le lait. Les pièces ont servi à les prendre. Le fromage, puis le fruit. Oui. On achète avec ça. Sarah essuie un copeau de sciure. Il était collé à la semelle. Le sol était tout jaune. C'est les halles. Bravo, Sarah. Le pilier de fer reste froid. Un rayon glisse encore sur la toile. Tu as fini de porter le cabas ? Il est un peu lourd. On le porte à deux. Sarah tient une anse. Papa tient l'autre. La poire roule un peu, puis s'arrête. Elle reste. Oui. On rentre ? Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1603,7 +1662,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1679,10 +1738,31 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Louna a compris. Le travail de maman sert. L'argent sert à acheter. Pain. Légumes. Chaussures.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le cabas tient le fromage et la poire.
+narrateur|Le papier huilé sent encore le lait.
+maman|Les pièces ont servi à les prendre.
+enfant-f|Le fromage, puis le fruit.
+papa|Oui.
+papa|On achète avec ça.
+narrateur|Sarah essuie un copeau de sciure.
+narrateur|Il était collé à la semelle.
+enfant-f|Le sol était tout jaune.
+maman|C'est les halles.
+maman|Bravo, Sarah.
+narrateur|Le pilier de fer reste froid.
+narrateur|Un rayon glisse encore sur la toile.
+papa|Tu as fini de porter le cabas ?
+enfant-f|Il est un peu lourd.
+maman|On le porte à deux.
+narrateur|Sarah tient une anse.
+narrateur|Papa tient l'autre.
+narrateur|La poire roule un peu, puis s'arrête.
+enfant-f|Elle reste.
+papa|Oui.
+maman|On rentre ?
+enfant-f|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1707,12 +1787,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>À la maison, Louna pose le pain. Papa range les légumes.</t>
+          <t>La table de la cuisine est claire. Sarah pose le papier huilé. Le fromage est blanc, un peu gras. Tu poses la poire à côté ? Oui. La poire a une tache dorée. On goûte le fromage ? Un tout petit bout. Sarah goûte. C'est doux, un peu salé. C'est bon. Merci d'avoir ramassé la poire. Maman coupe la poire en quartiers. Le jus brille sur la planche. Elle sent le sucre. Oui. Un copeau de sciure tombe du cabas. Sarah le pose près de la fenêtre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;À la maison, Louna pose le pain. Papa range les légumes.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La table de la cuisine est claire. Sarah pose le papier huilé. Le fromage est blanc, un peu gras. Tu poses la poire à côté ? Oui. La poire a une tache dorée. On goûte le fromage ? Un tout petit bout. Sarah goûte. C'est doux, un peu salé. C'est bon. Merci d'avoir ramassé la poire. Maman coupe la poire en quartiers. Le jus brille sur la planche. Elle sent le sucre. Oui. Un copeau de sciure tombe du cabas. Sarah le pose près de la fenêtre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1775,7 +1855,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1843,10 +1923,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|À la maison, Louna pose le pain. Papa range les légumes.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|La table de la cuisine est claire.
+narrateur|Sarah pose le papier huilé.
+narrateur|Le fromage est blanc, un peu gras.
+papa|Tu poses la poire à côté ?
+enfant-f|Oui.
+narrateur|La poire a une tache dorée.
+enfant-f|On goûte le fromage ?
+maman|Un tout petit bout.
+narrateur|Sarah goûte.
+narrateur|C'est doux, un peu salé.
+enfant-f|C'est bon.
+papa|Merci d'avoir ramassé la poire.
+narrateur|Maman coupe la poire en quartiers.
+narrateur|Le jus brille sur la planche.
+enfant-f|Elle sent le sucre.
+maman|Oui.
+narrateur|Un copeau de sciure tombe du cabas.
+narrateur|Sarah le pose près de la fenêtre.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1871,12 +1967,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a le fromage. On a la poire aussi. Bravo, Sarah. Deux choses, sous les halles. La poire sent le sucre, tout près.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>On a le fromage. On a la poire aussi. Bravo, Sarah. Deux choses, sous les halles. La poire sent le sucre, tout près.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1939,7 +2035,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2011,10 +2107,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|On a le fromage.
+enfant-f|On a la poire aussi.
+maman|Bravo, Sarah.
+papa|Deux choses, sous les halles.
+narrateur|La poire sent le sucre, tout près.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2033,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2170,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.ARG.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>boulangerie puis marché</t>
+          <t>halles, sciure au sol, piliers de fer, stand du fromage puis des poires</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Louna, maman, papa</t>
+          <t>Sarah, maman, papa</t>
         </is>
       </c>
     </row>
